--- a/tiflow-bfarm/build/0.9.0/all-profiles.xlsx
+++ b/tiflow-bfarm/build/0.9.0/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T08:45:49+00:00</t>
+    <t>2026-03-24T17:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
